--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/2-Decision-Tables/ExternalElements.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/2-Decision-Tables/ExternalElements.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I72"/>
+  <dimension ref="B2:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1161,77 +1161,87 @@
     <row r="63">
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Method String[] BorrowerMessages(Integer borrowerAge, Double borrowerIncome)</t>
-        </is>
-      </c>
+          <t>Spreadsheet String[] BorrowerMessages(Integer borrowerAge, Double borrowerIncome)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>Borrower borrower = new Borrower(age = borrowerAge, income = borrowerIncome);</t>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>return ValidateBorrower(borrower, new CheckResult()).messages;</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="3" t="inlineStr">
+          <t>Borrower</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>= new Borrower(age = borrowerAge, income = borrowerIncome)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>= ValidateBorrower($Borrower, new CheckResult()).messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Test BorrowerMessages BorrowerMessagesTest</t>
         </is>
       </c>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="7" t="inlineStr">
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>borrowerAge</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>borrowerIncome</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="8" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Messages</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>Too young, No income</t>
         </is>
       </c>
     </row>
@@ -1240,42 +1250,56 @@
         <v>16</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Too young</t>
+          <t>Too young, No income</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="5" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C72" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="D72" s="9" t="n"/>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Too young</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D73" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="B42:D42"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="B40:I40"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="C15:D15"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B57:D57"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B63:C63"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
